--- a/samples/premium-comparison/premium_corrige.xlsx
+++ b/samples/premium-comparison/premium_corrige.xlsx
@@ -141,19 +141,19 @@
     <t>Q11</t>
   </si>
   <si>
-    <t>S03 : 361 711,45 € ; S04 : -47 241,93 € (déficitaire).</t>
+    <t>S03 : 361 711,45 € ; S04 : -47 241,93 €.</t>
   </si>
   <si>
     <t>Q12</t>
   </si>
   <si>
-    <t>VRAIE. Ratio trafic ×2,64 &gt; produit des leviers commerciaux (transfo × panier) ×1,69. Le trafic explique 65 % de l'écart (échelle log) contre 34,9 % pour transformation + panier. La fréquentation (emplacement, vitrine, horaires) est surtout subie ; transformation et panier sont les leviers pilotables.</t>
+    <t>VRAIE. Ratio trafic ×2,64 &gt; produit des leviers commerciaux (transfo × panier) ×1,69. Le trafic explique 65 % de l'écart (échelle log) contre 34,9 % pour transformation + panier. La fréquentation est surtout subie ; transformation et panier sont les leviers pilotables.</t>
   </si>
   <si>
     <t>Q13</t>
   </si>
   <si>
-    <t>RÉFUTÉE. S04 est même plus petit ou comparable (62 vs 68 m²) mais son CA/m² est 4,06× plus faible et son CA/vendeur 3,56× plus faible : l'écart PERSISTE après normalisation, donc c'est une vraie sous-performance, pas un effet de taille. Actions : (1) sur le trafic — campagne locale / vitrine / alignement des horaires ; (2) sur un levier pilotable — formation à la vente additionnelle (articles/ticket 1,22 vs 1,41) et montée en gamme du panier.</t>
+    <t>RÉFUTÉE. S04 (62 vs 68 m²) a un CA/m² ×4,06 plus faible et un CA/vendeur ×3,56 plus faible : l'écart PERSISTE après normalisation, donc vraie sous-performance, pas un effet de taille. Actions : (1) trafic — campagne locale / vitrine / horaires ; (2) levier pilotable — vente additionnelle (articles/ticket 1,22 vs 1,41) et montée en gamme du panier.</t>
   </si>
   <si>
     <t>Décomposition de l'écart de CA</t>
